--- a/product_selector_out/STM32F101 - diff.xlsx
+++ b/product_selector_out/STM32F101 - diff.xlsx
@@ -713,17 +713,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -994,17 +994,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -1448,17 +1448,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">

--- a/product_selector_out/STM32F101 - diff.xlsx
+++ b/product_selector_out/STM32F101 - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1856</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1792</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="18">
